--- a/event_registration_forms/029_festival_kickoff_reception_rsvp_form--event_registration_forms.xlsx
+++ b/event_registration_forms/029_festival_kickoff_reception_rsvp_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'guest_1',_'label':_'guest_1'}</t>
+          <t>guest_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 1', 'label': 'Guest 1'}</t>
+          <t>Guest 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'guest_2',_'label':_'guest_2'}</t>
+          <t>guest_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 2', 'label': 'Guest 2'}</t>
+          <t>Guest 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'guest_3',_'label':_'guest_3'}</t>
+          <t>guest_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 3', 'label': 'Guest 3'}</t>
+          <t>Guest 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'guest_4',_'label':_'guest_4'}</t>
+          <t>guest_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 4', 'label': 'Guest 4'}</t>
+          <t>Guest 4</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'mail',_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Mail', 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'onsite',_'label':_'onsite'}</t>
+          <t>onsite</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Onsite', 'label': 'Onsite'}</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'mail',_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Mail', 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'onsite',_'label':_'onsite'}</t>
+          <t>onsite</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Onsite', 'label': 'Onsite'}</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'guest_1',_'label':_'guest_1'}</t>
+          <t>guest_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 1', 'label': 'Guest 1'}</t>
+          <t>Guest 1</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'guest_2',_'label':_'guest_2'}</t>
+          <t>guest_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 2', 'label': 'Guest 2'}</t>
+          <t>Guest 2</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'guest_3',_'label':_'guest_3'}</t>
+          <t>guest_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 3', 'label': 'Guest 3'}</t>
+          <t>Guest 3</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'guest_4',_'label':_'guest_4'}</t>
+          <t>guest_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Guest 4', 'label': 'Guest 4'}</t>
+          <t>Guest 4</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_720,_'label':_720}</t>
+          <t>720</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 720, 'label': 720}</t>
+          <t>720</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_780,_'label':_780}</t>
+          <t>780</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 780, 'label': 780}</t>
+          <t>780</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_840,_'label':_840}</t>
+          <t>840</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 840, 'label': 840}</t>
+          <t>840</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'location_1',_'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Location 1', 'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'location_2',_'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Location 2', 'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'mail',_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Mail', 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'onsite',_'label':_'onsite'}</t>
+          <t>onsite</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Onsite', 'label': 'Onsite'}</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'mail',_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Mail', 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'onsite',_'label':_'onsite'}</t>
+          <t>onsite</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Onsite', 'label': 'Onsite'}</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
